--- a/docs/v2/진행현황-간트차트.xlsx
+++ b/docs/v2/진행현황-간트차트.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -117,6 +117,16 @@
       <b val="1"/>
       <color rgb="001F2937"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001B7A4A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="10">
@@ -237,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -300,6 +310,21 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -665,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T47"/>
+  <dimension ref="A1:T58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -700,7 +725,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일: 2026-07-31 · 용어·코드 정의는 '용어·코드 설명' 탭, 병원용 변경 항목은 '병원용 변경 검토' 탭 참조</t>
+          <t>기준일: 2026-08-05 · 용어·코드 정의는 '용어·코드 설명' 탭, 병원용 변경 항목은 '병원용 변경 검토' 탭 참조</t>
         </is>
       </c>
     </row>
@@ -1299,433 +1324,357 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>v1 마무리 — 인사이트용 (8월 마감 목표)</t>
+          <t>[완료] 7단계 — 지표·구조 재편 (08/01~05)</t>
         </is>
       </c>
       <c r="B19" s="11" t="n"/>
       <c r="C19" s="11" t="n"/>
       <c r="D19" s="11" t="n"/>
       <c r="E19" s="12" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="13" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
-      <c r="L19" s="13" t="n"/>
-      <c r="M19" s="13" t="n"/>
-      <c r="N19" s="13" t="n"/>
-      <c r="O19" s="13" t="n"/>
-      <c r="P19" s="13" t="n"/>
-      <c r="Q19" s="13" t="n"/>
-      <c r="R19" s="13" t="n"/>
-      <c r="S19" s="13" t="n"/>
-      <c r="T19" s="13" t="n"/>
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="38" t="n"/>
+      <c r="H19" s="38" t="n"/>
+      <c r="I19" s="38" t="n"/>
+      <c r="J19" s="38" t="n"/>
+      <c r="K19" s="38" t="n"/>
+      <c r="L19" s="38" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="14" t="n"/>
+      <c r="A20" s="15" t="n"/>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>미입력 매출 5건 확정 입력</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>대기</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
+          <t>청구서·지출결의서 체크(미수금·발생 기준 지출) + 정기 매출·업무별 담당자</t>
+        </is>
+      </c>
+      <c r="C20" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="D20" s="41" t="inlineStr">
         <is>
           <t>AI 협업</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>확정 자료 수급 대기</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="14" t="n"/>
-      <c r="H20" s="14" t="n"/>
-      <c r="I20" s="14" t="n"/>
-      <c r="J20" s="21" t="n"/>
-      <c r="K20" s="21" t="n"/>
-      <c r="L20" s="14" t="n"/>
-      <c r="M20" s="14" t="n"/>
-      <c r="N20" s="14" t="n"/>
-      <c r="O20" s="14" t="n"/>
-      <c r="P20" s="14" t="n"/>
-      <c r="Q20" s="14" t="n"/>
-      <c r="R20" s="14" t="n"/>
-      <c r="S20" s="14" t="n"/>
-      <c r="T20" s="14" t="n"/>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>07-31~08-02</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="15" t="n"/>
+      <c r="I20" s="42" t="n"/>
+      <c r="J20" s="15" t="n"/>
+      <c r="K20" s="15" t="n"/>
+      <c r="L20" s="15" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="14" t="n"/>
+      <c r="A21" s="15" t="n"/>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>매출 자료 파서 고도화 — 카테고리 자동 추출·보고서 수익 반영</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
+          <t>신규→기존 자동 전환(계약 즉시) + 과거 33명 일괄 전환 + 매출 입력 딥링크</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="D21" s="41" t="inlineStr">
+        <is>
+          <t>AI 협업</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>08-03</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="15" t="n"/>
+      <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="n"/>
+      <c r="J21" s="42" t="n"/>
+      <c r="K21" s="15" t="n"/>
+      <c r="L21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="15" t="n"/>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Marketing ROAS 전환(3개월 이동 병기)·유입 코호트 전환율 위젯·혼합형 정기</t>
+        </is>
+      </c>
+      <c r="C22" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="D22" s="41" t="inlineStr">
+        <is>
+          <t>AI 협업</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>08-03~04</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="15" t="n"/>
+      <c r="H22" s="15" t="n"/>
+      <c r="I22" s="15" t="n"/>
+      <c r="J22" s="42" t="n"/>
+      <c r="K22" s="15" t="n"/>
+      <c r="L22" s="15" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>세부 유입경로·문의 서비스 구조화(기존분 백필) + 온라인 유입 퍼널 확장</t>
+        </is>
+      </c>
+      <c r="C23" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="D23" s="41" t="inlineStr">
+        <is>
+          <t>AI 협업</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>08-04</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="15" t="n"/>
+      <c r="H23" s="15" t="n"/>
+      <c r="I23" s="15" t="n"/>
+      <c r="J23" s="42" t="n"/>
+      <c r="K23" s="15" t="n"/>
+      <c r="L23" s="15" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="15" t="n"/>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>메뉴 재편(역할 기준 6그룹) + 알림 실이벤트 전환</t>
+        </is>
+      </c>
+      <c r="C24" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="D24" s="41" t="inlineStr">
+        <is>
+          <t>AI 협업</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>08-04</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
+      <c r="H24" s="15" t="n"/>
+      <c r="I24" s="15" t="n"/>
+      <c r="J24" s="42" t="n"/>
+      <c r="K24" s="15" t="n"/>
+      <c r="L24" s="15" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="15" t="n"/>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>광고 채널 연동 실데이터 전환(수집 상태·재수집·이력) + 외부 매출 연동 보류 처리</t>
+        </is>
+      </c>
+      <c r="C25" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="D25" s="41" t="inlineStr">
+        <is>
+          <t>AI 협업</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>08-05</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="15" t="n"/>
+      <c r="H25" s="15" t="n"/>
+      <c r="I25" s="15" t="n"/>
+      <c r="J25" s="42" t="n"/>
+      <c r="K25" s="15" t="n"/>
+      <c r="L25" s="15" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>v1 마무리 — 인사이트용 (8월 마감 목표)</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="13" t="n"/>
+      <c r="G26" s="13" t="n"/>
+      <c r="H26" s="13" t="n"/>
+      <c r="I26" s="13" t="n"/>
+      <c r="J26" s="13" t="n"/>
+      <c r="K26" s="13" t="n"/>
+      <c r="L26" s="13" t="n"/>
+      <c r="M26" s="13" t="n"/>
+      <c r="N26" s="13" t="n"/>
+      <c r="O26" s="13" t="n"/>
+      <c r="P26" s="13" t="n"/>
+      <c r="Q26" s="13" t="n"/>
+      <c r="R26" s="13" t="n"/>
+      <c r="S26" s="13" t="n"/>
+      <c r="T26" s="13" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="15" t="n"/>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>[긴급] 사용자 권한 페이지 정리 — 목 매트릭스 제거·역할별 권한 안내</t>
+        </is>
+      </c>
+      <c r="C27" s="43" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D27" s="41" t="inlineStr">
         <is>
           <t>AI 협업</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr"/>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="14" t="n"/>
-      <c r="H21" s="14" t="n"/>
-      <c r="I21" s="14" t="n"/>
-      <c r="J21" s="21" t="n"/>
-      <c r="K21" s="21" t="n"/>
-      <c r="L21" s="21" t="n"/>
-      <c r="M21" s="14" t="n"/>
-      <c r="N21" s="14" t="n"/>
-      <c r="O21" s="14" t="n"/>
-      <c r="P21" s="14" t="n"/>
-      <c r="Q21" s="14" t="n"/>
-      <c r="R21" s="14" t="n"/>
-      <c r="S21" s="14" t="n"/>
-      <c r="T21" s="14" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="14" t="n"/>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>백업 외부 복제(서버 외부 보관)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>최우선 — 진행 예약(투두 #46)</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="15" t="n"/>
+      <c r="H27" s="15" t="n"/>
+      <c r="I27" s="15" t="n"/>
+      <c r="J27" s="15" t="n"/>
+      <c r="K27" s="44" t="n"/>
+      <c r="L27" s="15" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="15" t="n"/>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>대시보드/분석 역할 분리 — 중복 위젯 4종 정리·딥링크</t>
+        </is>
+      </c>
+      <c r="C28" s="43" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D28" s="41" t="inlineStr">
         <is>
           <t>AI 협업</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr"/>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="14" t="n"/>
-      <c r="H22" s="14" t="n"/>
-      <c r="I22" s="14" t="n"/>
-      <c r="J22" s="21" t="n"/>
-      <c r="K22" s="21" t="n"/>
-      <c r="L22" s="14" t="n"/>
-      <c r="M22" s="14" t="n"/>
-      <c r="N22" s="14" t="n"/>
-      <c r="O22" s="14" t="n"/>
-      <c r="P22" s="14" t="n"/>
-      <c r="Q22" s="14" t="n"/>
-      <c r="R22" s="14" t="n"/>
-      <c r="S22" s="14" t="n"/>
-      <c r="T22" s="14" t="n"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="14" t="n"/>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>도메인 확보·정식 주소 전환</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>메뉴 재편 후속(P1)</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
+      <c r="H28" s="15" t="n"/>
+      <c r="I28" s="15" t="n"/>
+      <c r="J28" s="15" t="n"/>
+      <c r="K28" s="44" t="n"/>
+      <c r="L28" s="15" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="15" t="n"/>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>코호트 위젯 표현 개선(가로 막대 → 세로 막대)</t>
+        </is>
+      </c>
+      <c r="C29" s="43" t="inlineStr">
+        <is>
+          <t>검토 중</t>
+        </is>
+      </c>
+      <c r="D29" s="41" t="inlineStr">
         <is>
           <t>AI 협업</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>현재 임시 주소 사용 중</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="14" t="n"/>
-      <c r="H23" s="14" t="n"/>
-      <c r="I23" s="14" t="n"/>
-      <c r="J23" s="14" t="n"/>
-      <c r="K23" s="21" t="n"/>
-      <c r="L23" s="21" t="n"/>
-      <c r="M23" s="21" t="n"/>
-      <c r="N23" s="14" t="n"/>
-      <c r="O23" s="14" t="n"/>
-      <c r="P23" s="14" t="n"/>
-      <c r="Q23" s="14" t="n"/>
-      <c r="R23" s="14" t="n"/>
-      <c r="S23" s="14" t="n"/>
-      <c r="T23" s="14" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="14" t="n"/>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>팀 사용 피드백 반영·화면 다듬기</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>표현법 확정 대기(투두 #43)</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
+      <c r="H29" s="15" t="n"/>
+      <c r="I29" s="15" t="n"/>
+      <c r="J29" s="15" t="n"/>
+      <c r="K29" s="44" t="n"/>
+      <c r="L29" s="15" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="15" t="n"/>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>외부 매출 연동 — 파일 업로드(선행) → 시트 연동</t>
+        </is>
+      </c>
+      <c r="C30" s="43" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="D30" s="41" t="inlineStr">
         <is>
           <t>AI 협업</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>운영 중 수시</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="14" t="n"/>
-      <c r="H24" s="14" t="n"/>
-      <c r="I24" s="14" t="n"/>
-      <c r="J24" s="21" t="n"/>
-      <c r="K24" s="21" t="n"/>
-      <c r="L24" s="21" t="n"/>
-      <c r="M24" s="21" t="n"/>
-      <c r="N24" s="21" t="n"/>
-      <c r="O24" s="14" t="n"/>
-      <c r="P24" s="14" t="n"/>
-      <c r="Q24" s="14" t="n"/>
-      <c r="R24" s="14" t="n"/>
-      <c r="S24" s="14" t="n"/>
-      <c r="T24" s="14" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="14" t="n"/>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>8월 월간 데이터 갱신 사이클 1회 완주(절차 최종 검증)</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>AI 협업</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr"/>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="14" t="n"/>
-      <c r="H25" s="14" t="n"/>
-      <c r="I25" s="14" t="n"/>
-      <c r="J25" s="14" t="n"/>
-      <c r="K25" s="14" t="n"/>
-      <c r="L25" s="14" t="n"/>
-      <c r="M25" s="14" t="n"/>
-      <c r="N25" s="21" t="n"/>
-      <c r="O25" s="14" t="n"/>
-      <c r="P25" s="14" t="n"/>
-      <c r="Q25" s="14" t="n"/>
-      <c r="R25" s="14" t="n"/>
-      <c r="S25" s="14" t="n"/>
-      <c r="T25" s="14" t="n"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="14" t="n"/>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>v1 마감 — 운영 안정판 확정·문서 정리</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>AI 협업</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>9월 초 목표</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="14" t="n"/>
-      <c r="H26" s="14" t="n"/>
-      <c r="I26" s="14" t="n"/>
-      <c r="J26" s="14" t="n"/>
-      <c r="K26" s="14" t="n"/>
-      <c r="L26" s="14" t="n"/>
-      <c r="M26" s="14" t="n"/>
-      <c r="N26" s="21" t="n"/>
-      <c r="O26" s="21" t="n"/>
-      <c r="P26" s="14" t="n"/>
-      <c r="Q26" s="14" t="n"/>
-      <c r="R26" s="14" t="n"/>
-      <c r="S26" s="14" t="n"/>
-      <c r="T26" s="14" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>v2-A — 인사이트용 고도화 (2차 출시 검토 항목)</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="13" t="n"/>
-      <c r="H27" s="13" t="n"/>
-      <c r="I27" s="13" t="n"/>
-      <c r="J27" s="13" t="n"/>
-      <c r="K27" s="13" t="n"/>
-      <c r="L27" s="13" t="n"/>
-      <c r="M27" s="13" t="n"/>
-      <c r="N27" s="13" t="n"/>
-      <c r="O27" s="13" t="n"/>
-      <c r="P27" s="13" t="n"/>
-      <c r="Q27" s="13" t="n"/>
-      <c r="R27" s="13" t="n"/>
-      <c r="S27" s="13" t="n"/>
-      <c r="T27" s="13" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="14" t="n"/>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>[선행] 실사용 데이터 축적 3개월</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="inlineStr">
-        <is>
-          <t>진행 중</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>7월 실가동 기준 → 10월 충족</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="23" t="n"/>
-      <c r="H28" s="23" t="n"/>
-      <c r="I28" s="23" t="n"/>
-      <c r="J28" s="23" t="n"/>
-      <c r="K28" s="23" t="n"/>
-      <c r="L28" s="23" t="n"/>
-      <c r="M28" s="23" t="n"/>
-      <c r="N28" s="23" t="n"/>
-      <c r="O28" s="23" t="n"/>
-      <c r="P28" s="23" t="n"/>
-      <c r="Q28" s="14" t="n"/>
-      <c r="R28" s="14" t="n"/>
-      <c r="S28" s="14" t="n"/>
-      <c r="T28" s="14" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="14" t="n"/>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>[선행] 행동 데이터 수집 설계(문의 횟수·단계 이동 패턴)</t>
-        </is>
-      </c>
-      <c r="C29" s="24" t="inlineStr">
-        <is>
-          <t>계획</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>AI 협업</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>축적 데이터 기반</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="14" t="n"/>
-      <c r="H29" s="14" t="n"/>
-      <c r="I29" s="14" t="n"/>
-      <c r="J29" s="14" t="n"/>
-      <c r="K29" s="14" t="n"/>
-      <c r="L29" s="14" t="n"/>
-      <c r="M29" s="14" t="n"/>
-      <c r="N29" s="14" t="n"/>
-      <c r="O29" s="25" t="n"/>
-      <c r="P29" s="25" t="n"/>
-      <c r="Q29" s="14" t="n"/>
-      <c r="R29" s="14" t="n"/>
-      <c r="S29" s="14" t="n"/>
-      <c r="T29" s="14" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="14" t="n"/>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>광고 성과 귀속 고도화 — 채널·캠페인별 수익 분해</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="inlineStr">
-        <is>
-          <t>계획</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>AI 협업</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>문의의 광고 출처 증거(UTM) 축적 필요</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="14" t="n"/>
-      <c r="H30" s="14" t="n"/>
-      <c r="I30" s="14" t="n"/>
-      <c r="J30" s="14" t="n"/>
-      <c r="K30" s="14" t="n"/>
-      <c r="L30" s="14" t="n"/>
-      <c r="M30" s="14" t="n"/>
-      <c r="N30" s="14" t="n"/>
-      <c r="O30" s="25" t="n"/>
-      <c r="P30" s="25" t="n"/>
-      <c r="Q30" s="25" t="n"/>
-      <c r="R30" s="14" t="n"/>
-      <c r="S30" s="14" t="n"/>
-      <c r="T30" s="14" t="n"/>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>보안 검토 완료·재개 시 착수(투두 #45)</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="15" t="n"/>
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="15" t="n"/>
+      <c r="K30" s="15" t="n"/>
+      <c r="L30" s="15" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="14" t="n"/>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>잠재고객 자동 점수화·우선순위 지정(리드 스코어링)</t>
-        </is>
-      </c>
-      <c r="C31" s="24" t="inlineStr">
-        <is>
-          <t>계획</t>
+          <t>미입력 매출 5건 확정 입력</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>대기</t>
         </is>
       </c>
       <c r="D31" s="17" t="inlineStr">
@@ -1735,22 +1684,22 @@
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>2차 출시 검토 항목</t>
+          <t>확정 자료 수급 대기</t>
         </is>
       </c>
       <c r="F31" s="14" t="n"/>
       <c r="G31" s="14" t="n"/>
       <c r="H31" s="14" t="n"/>
       <c r="I31" s="14" t="n"/>
-      <c r="J31" s="14" t="n"/>
-      <c r="K31" s="14" t="n"/>
+      <c r="J31" s="21" t="n"/>
+      <c r="K31" s="21" t="n"/>
       <c r="L31" s="14" t="n"/>
       <c r="M31" s="14" t="n"/>
       <c r="N31" s="14" t="n"/>
       <c r="O31" s="14" t="n"/>
       <c r="P31" s="14" t="n"/>
-      <c r="Q31" s="25" t="n"/>
-      <c r="R31" s="25" t="n"/>
+      <c r="Q31" s="14" t="n"/>
+      <c r="R31" s="14" t="n"/>
       <c r="S31" s="14" t="n"/>
       <c r="T31" s="14" t="n"/>
     </row>
@@ -1758,12 +1707,12 @@
       <c r="A32" s="14" t="n"/>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>개인화 커뮤니케이션 도구(세그먼트 메시지·알림톡)</t>
-        </is>
-      </c>
-      <c r="C32" s="24" t="inlineStr">
-        <is>
-          <t>계획</t>
+          <t>매출 자료 파서 고도화 — 카테고리 자동 추출·보고서 수익 반영</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>예정</t>
         </is>
       </c>
       <c r="D32" s="17" t="inlineStr">
@@ -1771,37 +1720,33 @@
           <t>AI 협업</t>
         </is>
       </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>2차 출시 검토 항목</t>
-        </is>
-      </c>
+      <c r="E32" s="18" t="inlineStr"/>
       <c r="F32" s="14" t="n"/>
       <c r="G32" s="14" t="n"/>
       <c r="H32" s="14" t="n"/>
       <c r="I32" s="14" t="n"/>
-      <c r="J32" s="14" t="n"/>
-      <c r="K32" s="14" t="n"/>
-      <c r="L32" s="14" t="n"/>
+      <c r="J32" s="21" t="n"/>
+      <c r="K32" s="21" t="n"/>
+      <c r="L32" s="21" t="n"/>
       <c r="M32" s="14" t="n"/>
       <c r="N32" s="14" t="n"/>
       <c r="O32" s="14" t="n"/>
       <c r="P32" s="14" t="n"/>
       <c r="Q32" s="14" t="n"/>
-      <c r="R32" s="25" t="n"/>
-      <c r="S32" s="25" t="n"/>
+      <c r="R32" s="14" t="n"/>
+      <c r="S32" s="14" t="n"/>
       <c r="T32" s="14" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="14" t="n"/>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>보고서 고도화(PDF 서버 생성·차트 고정 저장) · 권한 세분화</t>
-        </is>
-      </c>
-      <c r="C33" s="24" t="inlineStr">
-        <is>
-          <t>계획</t>
+          <t>백업 외부 복제(서버 외부 보관)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>예정</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
@@ -1814,75 +1759,71 @@
       <c r="G33" s="14" t="n"/>
       <c r="H33" s="14" t="n"/>
       <c r="I33" s="14" t="n"/>
-      <c r="J33" s="14" t="n"/>
-      <c r="K33" s="14" t="n"/>
+      <c r="J33" s="21" t="n"/>
+      <c r="K33" s="21" t="n"/>
       <c r="L33" s="14" t="n"/>
       <c r="M33" s="14" t="n"/>
       <c r="N33" s="14" t="n"/>
       <c r="O33" s="14" t="n"/>
       <c r="P33" s="14" t="n"/>
-      <c r="Q33" s="25" t="n"/>
-      <c r="R33" s="25" t="n"/>
+      <c r="Q33" s="14" t="n"/>
+      <c r="R33" s="14" t="n"/>
       <c r="S33" s="14" t="n"/>
       <c r="T33" s="14" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>v2-B — 병원용 신규 (인사이트용을 프로토타입으로, 내부팀 직접 개발 · AI 코딩 제외)</t>
-        </is>
-      </c>
+      <c r="A34" s="14" t="n"/>
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="11" t="n"/>
       <c r="E34" s="12" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="13" t="n"/>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="13" t="n"/>
-      <c r="L34" s="13" t="n"/>
-      <c r="M34" s="13" t="n"/>
-      <c r="N34" s="13" t="n"/>
-      <c r="O34" s="13" t="n"/>
-      <c r="P34" s="13" t="n"/>
-      <c r="Q34" s="13" t="n"/>
-      <c r="R34" s="13" t="n"/>
-      <c r="S34" s="13" t="n"/>
-      <c r="T34" s="13" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="14" t="n"/>
+      <c r="I34" s="14" t="n"/>
+      <c r="J34" s="14" t="n"/>
+      <c r="K34" s="21" t="n"/>
+      <c r="L34" s="21" t="n"/>
+      <c r="M34" s="21" t="n"/>
+      <c r="N34" s="14" t="n"/>
+      <c r="O34" s="14" t="n"/>
+      <c r="P34" s="14" t="n"/>
+      <c r="Q34" s="14" t="n"/>
+      <c r="R34" s="14" t="n"/>
+      <c r="S34" s="14" t="n"/>
+      <c r="T34" s="14" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="14" t="n"/>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>① 병의원 적합화 검토 — 기능 갭 분석(고객 개체·퍼널·규제·지표)</t>
-        </is>
-      </c>
-      <c r="C35" s="26" t="inlineStr">
+          <t>팀 사용 피드백 반영·화면 다듬기</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
       <c r="D35" s="17" t="inlineStr">
         <is>
-          <t>AI 협업+내부팀</t>
+          <t>AI 협업</t>
         </is>
       </c>
       <c r="E35" s="18" t="inlineStr">
         <is>
-          <t>'병원용 변경 검토' 탭이 출발점</t>
+          <t>운영 중 수시</t>
         </is>
       </c>
       <c r="F35" s="14" t="n"/>
       <c r="G35" s="14" t="n"/>
       <c r="H35" s="14" t="n"/>
       <c r="I35" s="14" t="n"/>
-      <c r="J35" s="27" t="n"/>
-      <c r="K35" s="27" t="n"/>
-      <c r="L35" s="27" t="n"/>
-      <c r="M35" s="27" t="n"/>
-      <c r="N35" s="27" t="n"/>
+      <c r="J35" s="21" t="n"/>
+      <c r="K35" s="21" t="n"/>
+      <c r="L35" s="21" t="n"/>
+      <c r="M35" s="21" t="n"/>
+      <c r="N35" s="21" t="n"/>
       <c r="O35" s="14" t="n"/>
       <c r="P35" s="14" t="n"/>
       <c r="Q35" s="14" t="n"/>
@@ -1894,10 +1835,10 @@
       <c r="A36" s="14" t="n"/>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>② 프로토타입 인계 패키지 — 화면·API 명세·도메인 규칙 문서화</t>
-        </is>
-      </c>
-      <c r="C36" s="26" t="inlineStr">
+          <t>8월 월간 데이터 갱신 사이클 1회 완주(절차 최종 검증)</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
@@ -1907,21 +1848,17 @@
           <t>AI 협업</t>
         </is>
       </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>인사이트용 = 프로토타입</t>
-        </is>
-      </c>
+      <c r="E36" s="18" t="inlineStr"/>
       <c r="F36" s="14" t="n"/>
       <c r="G36" s="14" t="n"/>
       <c r="H36" s="14" t="n"/>
       <c r="I36" s="14" t="n"/>
       <c r="J36" s="14" t="n"/>
-      <c r="K36" s="27" t="n"/>
-      <c r="L36" s="27" t="n"/>
-      <c r="M36" s="27" t="n"/>
-      <c r="N36" s="27" t="n"/>
-      <c r="O36" s="27" t="n"/>
+      <c r="K36" s="14" t="n"/>
+      <c r="L36" s="14" t="n"/>
+      <c r="M36" s="14" t="n"/>
+      <c r="N36" s="21" t="n"/>
+      <c r="O36" s="14" t="n"/>
       <c r="P36" s="14" t="n"/>
       <c r="Q36" s="14" t="n"/>
       <c r="R36" s="14" t="n"/>
@@ -1932,22 +1869,22 @@
       <c r="A37" s="14" t="n"/>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>③ 병원용 요구사항 확정 (변경사항 우선순위 확정)</t>
-        </is>
-      </c>
-      <c r="C37" s="26" t="inlineStr">
+          <t>v1 마감 — 운영 안정판 확정·문서 정리</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
       <c r="D37" s="17" t="inlineStr">
         <is>
-          <t>내부 디자인·개발팀</t>
+          <t>AI 협업</t>
         </is>
       </c>
       <c r="E37" s="18" t="inlineStr">
         <is>
-          <t>①·② 산출물 기반</t>
+          <t>9월 초 목표</t>
         </is>
       </c>
       <c r="F37" s="14" t="n"/>
@@ -1958,8 +1895,8 @@
       <c r="K37" s="14" t="n"/>
       <c r="L37" s="14" t="n"/>
       <c r="M37" s="14" t="n"/>
-      <c r="N37" s="14" t="n"/>
-      <c r="O37" s="27" t="n"/>
+      <c r="N37" s="21" t="n"/>
+      <c r="O37" s="21" t="n"/>
       <c r="P37" s="14" t="n"/>
       <c r="Q37" s="14" t="n"/>
       <c r="R37" s="14" t="n"/>
@@ -1967,101 +1904,89 @@
       <c r="T37" s="14" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="14" t="n"/>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>④ 병원용 UI/UX 디자인 (프로토타입 기반 재설계)</t>
-        </is>
-      </c>
-      <c r="C38" s="26" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>내부 디자인팀</t>
-        </is>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>환자·예약 중심 화면</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="n"/>
-      <c r="G38" s="14" t="n"/>
-      <c r="H38" s="14" t="n"/>
-      <c r="I38" s="14" t="n"/>
-      <c r="J38" s="14" t="n"/>
-      <c r="K38" s="14" t="n"/>
-      <c r="L38" s="14" t="n"/>
-      <c r="M38" s="14" t="n"/>
-      <c r="N38" s="14" t="n"/>
-      <c r="O38" s="27" t="n"/>
-      <c r="P38" s="27" t="n"/>
-      <c r="Q38" s="14" t="n"/>
-      <c r="R38" s="14" t="n"/>
-      <c r="S38" s="14" t="n"/>
-      <c r="T38" s="14" t="n"/>
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>v2-A — 인사이트용 고도화 (2차 출시 검토 항목)</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="13" t="n"/>
+      <c r="G38" s="13" t="n"/>
+      <c r="H38" s="13" t="n"/>
+      <c r="I38" s="13" t="n"/>
+      <c r="J38" s="13" t="n"/>
+      <c r="K38" s="13" t="n"/>
+      <c r="L38" s="13" t="n"/>
+      <c r="M38" s="13" t="n"/>
+      <c r="N38" s="13" t="n"/>
+      <c r="O38" s="13" t="n"/>
+      <c r="P38" s="13" t="n"/>
+      <c r="Q38" s="13" t="n"/>
+      <c r="R38" s="13" t="n"/>
+      <c r="S38" s="13" t="n"/>
+      <c r="T38" s="13" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="14" t="n"/>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>⑤ 병원용 개발 — 직접 프로그래밍 (AI 바이브 코딩 제외)</t>
-        </is>
-      </c>
-      <c r="C39" s="26" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>[선행] 실사용 데이터 축적 3개월</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>진행 중</t>
         </is>
       </c>
       <c r="D39" s="17" t="inlineStr">
         <is>
-          <t>내부 개발팀</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E39" s="18" t="inlineStr">
         <is>
-          <t>변경사항 순차 적용</t>
+          <t>7월 실가동 기준 → 10월 충족</t>
         </is>
       </c>
       <c r="F39" s="14" t="n"/>
-      <c r="G39" s="14" t="n"/>
-      <c r="H39" s="14" t="n"/>
-      <c r="I39" s="14" t="n"/>
-      <c r="J39" s="14" t="n"/>
-      <c r="K39" s="14" t="n"/>
-      <c r="L39" s="14" t="n"/>
-      <c r="M39" s="14" t="n"/>
-      <c r="N39" s="14" t="n"/>
-      <c r="O39" s="14" t="n"/>
-      <c r="P39" s="27" t="n"/>
-      <c r="Q39" s="27" t="n"/>
-      <c r="R39" s="27" t="n"/>
-      <c r="S39" s="27" t="n"/>
+      <c r="G39" s="23" t="n"/>
+      <c r="H39" s="23" t="n"/>
+      <c r="I39" s="23" t="n"/>
+      <c r="J39" s="23" t="n"/>
+      <c r="K39" s="23" t="n"/>
+      <c r="L39" s="23" t="n"/>
+      <c r="M39" s="23" t="n"/>
+      <c r="N39" s="23" t="n"/>
+      <c r="O39" s="23" t="n"/>
+      <c r="P39" s="23" t="n"/>
+      <c r="Q39" s="14" t="n"/>
+      <c r="R39" s="14" t="n"/>
+      <c r="S39" s="14" t="n"/>
       <c r="T39" s="14" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="14" t="n"/>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>⑥ 파일럿 병원 적용·피드백 반영</t>
-        </is>
-      </c>
-      <c r="C40" s="26" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>[선행] 행동 데이터 수집 설계(문의 횟수·단계 이동 패턴)</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>계획</t>
         </is>
       </c>
       <c r="D40" s="17" t="inlineStr">
         <is>
-          <t>내부 디자인·개발팀</t>
+          <t>AI 협업</t>
         </is>
       </c>
       <c r="E40" s="18" t="inlineStr">
         <is>
-          <t>1~2개 병원</t>
+          <t>축적 데이터 기반</t>
         </is>
       </c>
       <c r="F40" s="14" t="n"/>
@@ -2073,33 +1998,33 @@
       <c r="L40" s="14" t="n"/>
       <c r="M40" s="14" t="n"/>
       <c r="N40" s="14" t="n"/>
-      <c r="O40" s="14" t="n"/>
-      <c r="P40" s="14" t="n"/>
+      <c r="O40" s="25" t="n"/>
+      <c r="P40" s="25" t="n"/>
       <c r="Q40" s="14" t="n"/>
       <c r="R40" s="14" t="n"/>
-      <c r="S40" s="27" t="n"/>
+      <c r="S40" s="14" t="n"/>
       <c r="T40" s="14" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="14" t="n"/>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>⑦ 병원용 출시</t>
-        </is>
-      </c>
-      <c r="C41" s="26" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>광고 성과 귀속 고도화 — 채널·캠페인별 수익 분해</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>계획</t>
         </is>
       </c>
       <c r="D41" s="17" t="inlineStr">
         <is>
-          <t>내부 디자인·개발팀</t>
+          <t>AI 협업</t>
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr">
         <is>
-          <t>파일럿 통과 후</t>
+          <t>문의의 광고 출처 증거(UTM) 축적 필요</t>
         </is>
       </c>
       <c r="F41" s="14" t="n"/>
@@ -2111,56 +2036,457 @@
       <c r="L41" s="14" t="n"/>
       <c r="M41" s="14" t="n"/>
       <c r="N41" s="14" t="n"/>
-      <c r="O41" s="14" t="n"/>
-      <c r="P41" s="14" t="n"/>
-      <c r="Q41" s="14" t="n"/>
+      <c r="O41" s="25" t="n"/>
+      <c r="P41" s="25" t="n"/>
+      <c r="Q41" s="25" t="n"/>
       <c r="R41" s="14" t="n"/>
       <c r="S41" s="14" t="n"/>
-      <c r="T41" s="27" t="n"/>
+      <c r="T41" s="14" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="n"/>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>잠재고객 자동 점수화·우선순위 지정(리드 스코어링)</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>계획</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>AI 협업</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="inlineStr">
+        <is>
+          <t>2차 출시 검토 항목</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="n"/>
+      <c r="G42" s="14" t="n"/>
+      <c r="H42" s="14" t="n"/>
+      <c r="I42" s="14" t="n"/>
+      <c r="J42" s="14" t="n"/>
+      <c r="K42" s="14" t="n"/>
+      <c r="L42" s="14" t="n"/>
+      <c r="M42" s="14" t="n"/>
+      <c r="N42" s="14" t="n"/>
+      <c r="O42" s="14" t="n"/>
+      <c r="P42" s="14" t="n"/>
+      <c r="Q42" s="25" t="n"/>
+      <c r="R42" s="25" t="n"/>
+      <c r="S42" s="14" t="n"/>
+      <c r="T42" s="14" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="28" t="inlineStr">
+      <c r="A43" s="14" t="n"/>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>개인화 커뮤니케이션 도구(세그먼트 메시지·알림톡)</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>계획</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>AI 협업</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="inlineStr">
+        <is>
+          <t>2차 출시 검토 항목</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="n"/>
+      <c r="G43" s="14" t="n"/>
+      <c r="H43" s="14" t="n"/>
+      <c r="I43" s="14" t="n"/>
+      <c r="J43" s="14" t="n"/>
+      <c r="K43" s="14" t="n"/>
+      <c r="L43" s="14" t="n"/>
+      <c r="M43" s="14" t="n"/>
+      <c r="N43" s="14" t="n"/>
+      <c r="O43" s="14" t="n"/>
+      <c r="P43" s="14" t="n"/>
+      <c r="Q43" s="14" t="n"/>
+      <c r="R43" s="25" t="n"/>
+      <c r="S43" s="25" t="n"/>
+      <c r="T43" s="14" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="n"/>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>보고서 고도화(PDF 서버 생성·차트 고정 저장) · 권한 세분화</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>계획</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>AI 협업</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="inlineStr"/>
+      <c r="F44" s="14" t="n"/>
+      <c r="G44" s="14" t="n"/>
+      <c r="H44" s="14" t="n"/>
+      <c r="I44" s="14" t="n"/>
+      <c r="J44" s="14" t="n"/>
+      <c r="K44" s="14" t="n"/>
+      <c r="L44" s="14" t="n"/>
+      <c r="M44" s="14" t="n"/>
+      <c r="N44" s="14" t="n"/>
+      <c r="O44" s="14" t="n"/>
+      <c r="P44" s="14" t="n"/>
+      <c r="Q44" s="25" t="n"/>
+      <c r="R44" s="25" t="n"/>
+      <c r="S44" s="14" t="n"/>
+      <c r="T44" s="14" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>v2-B — 병원용 신규 (인사이트용을 프로토타입으로, 내부팀 직접 개발 · AI 코딩 제외)</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="12" t="n"/>
+      <c r="F45" s="13" t="n"/>
+      <c r="G45" s="13" t="n"/>
+      <c r="H45" s="13" t="n"/>
+      <c r="I45" s="13" t="n"/>
+      <c r="J45" s="13" t="n"/>
+      <c r="K45" s="13" t="n"/>
+      <c r="L45" s="13" t="n"/>
+      <c r="M45" s="13" t="n"/>
+      <c r="N45" s="13" t="n"/>
+      <c r="O45" s="13" t="n"/>
+      <c r="P45" s="13" t="n"/>
+      <c r="Q45" s="13" t="n"/>
+      <c r="R45" s="13" t="n"/>
+      <c r="S45" s="13" t="n"/>
+      <c r="T45" s="13" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="n"/>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>① 병의원 적합화 검토 — 기능 갭 분석(고객 개체·퍼널·규제·지표)</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
+        <is>
+          <t>AI 협업+내부팀</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>'병원용 변경 검토' 탭이 출발점</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="n"/>
+      <c r="G46" s="14" t="n"/>
+      <c r="H46" s="14" t="n"/>
+      <c r="I46" s="14" t="n"/>
+      <c r="J46" s="27" t="n"/>
+      <c r="K46" s="27" t="n"/>
+      <c r="L46" s="27" t="n"/>
+      <c r="M46" s="27" t="n"/>
+      <c r="N46" s="27" t="n"/>
+      <c r="O46" s="14" t="n"/>
+      <c r="P46" s="14" t="n"/>
+      <c r="Q46" s="14" t="n"/>
+      <c r="R46" s="14" t="n"/>
+      <c r="S46" s="14" t="n"/>
+      <c r="T46" s="14" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="n"/>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>② 프로토타입 인계 패키지 — 화면·API 명세·도메인 규칙 문서화</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="inlineStr">
+        <is>
+          <t>AI 협업</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="inlineStr">
+        <is>
+          <t>인사이트용 = 프로토타입</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="n"/>
+      <c r="G47" s="14" t="n"/>
+      <c r="H47" s="14" t="n"/>
+      <c r="I47" s="14" t="n"/>
+      <c r="J47" s="14" t="n"/>
+      <c r="K47" s="27" t="n"/>
+      <c r="L47" s="27" t="n"/>
+      <c r="M47" s="27" t="n"/>
+      <c r="N47" s="27" t="n"/>
+      <c r="O47" s="27" t="n"/>
+      <c r="P47" s="14" t="n"/>
+      <c r="Q47" s="14" t="n"/>
+      <c r="R47" s="14" t="n"/>
+      <c r="S47" s="14" t="n"/>
+      <c r="T47" s="14" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="n"/>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>③ 병원용 요구사항 확정 (변경사항 우선순위 확정)</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="inlineStr">
+        <is>
+          <t>내부 디자인·개발팀</t>
+        </is>
+      </c>
+      <c r="E48" s="18" t="inlineStr">
+        <is>
+          <t>①·② 산출물 기반</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="n"/>
+      <c r="G48" s="14" t="n"/>
+      <c r="H48" s="14" t="n"/>
+      <c r="I48" s="14" t="n"/>
+      <c r="J48" s="14" t="n"/>
+      <c r="K48" s="14" t="n"/>
+      <c r="L48" s="14" t="n"/>
+      <c r="M48" s="14" t="n"/>
+      <c r="N48" s="14" t="n"/>
+      <c r="O48" s="27" t="n"/>
+      <c r="P48" s="14" t="n"/>
+      <c r="Q48" s="14" t="n"/>
+      <c r="R48" s="14" t="n"/>
+      <c r="S48" s="14" t="n"/>
+      <c r="T48" s="14" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="n"/>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>④ 병원용 UI/UX 디자인 (프로토타입 기반 재설계)</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="D49" s="17" t="inlineStr">
+        <is>
+          <t>내부 디자인팀</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="inlineStr">
+        <is>
+          <t>환자·예약 중심 화면</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="n"/>
+      <c r="G49" s="14" t="n"/>
+      <c r="H49" s="14" t="n"/>
+      <c r="I49" s="14" t="n"/>
+      <c r="J49" s="14" t="n"/>
+      <c r="K49" s="14" t="n"/>
+      <c r="L49" s="14" t="n"/>
+      <c r="M49" s="14" t="n"/>
+      <c r="N49" s="14" t="n"/>
+      <c r="O49" s="27" t="n"/>
+      <c r="P49" s="27" t="n"/>
+      <c r="Q49" s="14" t="n"/>
+      <c r="R49" s="14" t="n"/>
+      <c r="S49" s="14" t="n"/>
+      <c r="T49" s="14" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="n"/>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>⑤ 병원용 개발 — 직접 프로그래밍 (AI 바이브 코딩 제외)</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>내부 개발팀</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>변경사항 순차 적용</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="n"/>
+      <c r="G50" s="14" t="n"/>
+      <c r="H50" s="14" t="n"/>
+      <c r="I50" s="14" t="n"/>
+      <c r="J50" s="14" t="n"/>
+      <c r="K50" s="14" t="n"/>
+      <c r="L50" s="14" t="n"/>
+      <c r="M50" s="14" t="n"/>
+      <c r="N50" s="14" t="n"/>
+      <c r="O50" s="14" t="n"/>
+      <c r="P50" s="27" t="n"/>
+      <c r="Q50" s="27" t="n"/>
+      <c r="R50" s="27" t="n"/>
+      <c r="S50" s="27" t="n"/>
+      <c r="T50" s="14" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="n"/>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>⑥ 파일럿 병원 적용·피드백 반영</t>
+        </is>
+      </c>
+      <c r="C51" s="26" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="D51" s="17" t="inlineStr">
+        <is>
+          <t>내부 디자인·개발팀</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>1~2개 병원</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="n"/>
+      <c r="G51" s="14" t="n"/>
+      <c r="H51" s="14" t="n"/>
+      <c r="I51" s="14" t="n"/>
+      <c r="J51" s="14" t="n"/>
+      <c r="K51" s="14" t="n"/>
+      <c r="L51" s="14" t="n"/>
+      <c r="M51" s="14" t="n"/>
+      <c r="N51" s="14" t="n"/>
+      <c r="O51" s="14" t="n"/>
+      <c r="P51" s="14" t="n"/>
+      <c r="Q51" s="14" t="n"/>
+      <c r="R51" s="14" t="n"/>
+      <c r="S51" s="27" t="n"/>
+      <c r="T51" s="14" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="n"/>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>⑦ 병원용 출시</t>
+        </is>
+      </c>
+      <c r="C52" s="26" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>내부 디자인·개발팀</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>파일럿 통과 후</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="n"/>
+      <c r="G52" s="14" t="n"/>
+      <c r="H52" s="14" t="n"/>
+      <c r="I52" s="14" t="n"/>
+      <c r="J52" s="14" t="n"/>
+      <c r="K52" s="14" t="n"/>
+      <c r="L52" s="14" t="n"/>
+      <c r="M52" s="14" t="n"/>
+      <c r="N52" s="14" t="n"/>
+      <c r="O52" s="14" t="n"/>
+      <c r="P52" s="14" t="n"/>
+      <c r="Q52" s="14" t="n"/>
+      <c r="R52" s="14" t="n"/>
+      <c r="S52" s="14" t="n"/>
+      <c r="T52" s="27" t="n"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="28" t="inlineStr">
         <is>
           <t>※ 완료 구간은 실제 완료된 주 기준. 예정 구간은 잠정 일정 — 자료 수급·내부팀 리소스에 따라 조정.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="28" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="28" t="inlineStr">
         <is>
           <t>※ v2-A(인사이트용)와 v2-B(병원용)는 동시 진행. 병원용은 인사이트용을 프로토타입으로 내부 디자인·개발팀이 직접 프로그래밍(AI 바이브 코딩 제외).</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="28" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="28" t="inlineStr">
         <is>
           <t>※ v2-B ①②(적합화 검토·인계 패키지)는 AI 협업으로 준비 → ③부터 내부팀 주도. 변경 검토 상세는 '병원용 변경 검토' 탭.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="28" t="inlineStr">
+    <row r="57">
+      <c r="B57" s="28" t="inlineStr">
         <is>
           <t>※ 참고 자산: 구시스템(치과 CRM)이 환자 퍼널(방문→상담→예약→내원→시술→매출)·예약 관리 기능의 원형 보유 — 병원용 개발 시 재활용 가능.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="28" t="inlineStr">
+    <row r="58">
+      <c r="B58" s="28" t="inlineStr">
         <is>
           <t>※ 시스템 현황: 운영 서버 가동 중 · 실데이터 운영(2년치 계약 355건·광고비 12개월) · 네이버·구글·메타 3채널 광고 자동 수집.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A27:E27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/v2/진행현황-간트차트.xlsx
+++ b/docs/v2/진행현황-간트차트.xlsx
@@ -1549,12 +1549,12 @@
       <c r="A27" s="15" t="n"/>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>[긴급] 사용자 권한 페이지 정리 — 목 매트릭스 제거·역할별 권한 안내</t>
-        </is>
-      </c>
-      <c r="C27" s="43" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>사용자 권한 페이지 정리 — 목 매트릭스 제거·역할별 권한 안내</t>
+        </is>
+      </c>
+      <c r="C27" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="D27" s="41" t="inlineStr">
@@ -1564,15 +1564,15 @@
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>최우선 — 진행 예약(투두 #46)</t>
+          <t>08-05</t>
         </is>
       </c>
       <c r="F27" s="15" t="n"/>
       <c r="G27" s="15" t="n"/>
       <c r="H27" s="15" t="n"/>
       <c r="I27" s="15" t="n"/>
-      <c r="J27" s="15" t="n"/>
-      <c r="K27" s="44" t="n"/>
+      <c r="J27" s="42" t="n"/>
+      <c r="K27" s="15" t="n"/>
       <c r="L27" s="15" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">

--- a/docs/v2/진행현황-간트차트.xlsx
+++ b/docs/v2/진행현황-간트차트.xlsx
@@ -1609,12 +1609,12 @@
       <c r="A29" s="15" t="n"/>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>코호트 위젯 표현 개선(가로 막대 → 세로 막대)</t>
-        </is>
-      </c>
-      <c r="C29" s="43" t="inlineStr">
-        <is>
-          <t>검토 중</t>
+          <t>코호트 위젯 표현 개선 — 시간축 세로 막대·% 상시 표기</t>
+        </is>
+      </c>
+      <c r="C29" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="D29" s="41" t="inlineStr">
@@ -1624,15 +1624,15 @@
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>표현법 확정 대기(투두 #43)</t>
+          <t>08-05</t>
         </is>
       </c>
       <c r="F29" s="15" t="n"/>
       <c r="G29" s="15" t="n"/>
       <c r="H29" s="15" t="n"/>
       <c r="I29" s="15" t="n"/>
-      <c r="J29" s="15" t="n"/>
-      <c r="K29" s="44" t="n"/>
+      <c r="J29" s="42" t="n"/>
+      <c r="K29" s="15" t="n"/>
       <c r="L29" s="15" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">

--- a/docs/v2/진행현황-간트차트.xlsx
+++ b/docs/v2/진행현황-간트차트.xlsx
@@ -1582,9 +1582,9 @@
           <t>대시보드/분석 역할 분리 — 중복 위젯 4종 정리·딥링크</t>
         </is>
       </c>
-      <c r="C28" s="43" t="inlineStr">
-        <is>
-          <t>예정</t>
+      <c r="C28" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="D28" s="41" t="inlineStr">
@@ -1594,15 +1594,15 @@
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>메뉴 재편 후속(P1)</t>
+          <t>08-06</t>
         </is>
       </c>
       <c r="F28" s="15" t="n"/>
       <c r="G28" s="15" t="n"/>
       <c r="H28" s="15" t="n"/>
       <c r="I28" s="15" t="n"/>
-      <c r="J28" s="15" t="n"/>
-      <c r="K28" s="44" t="n"/>
+      <c r="J28" s="42" t="n"/>
+      <c r="K28" s="15" t="n"/>
       <c r="L28" s="15" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">

--- a/docs/v2/진행현황-간트차트.xlsx
+++ b/docs/v2/진행현황-간트차트.xlsx
@@ -690,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T58"/>
+  <dimension ref="A1:T60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1324,7 +1324,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>[완료] 7단계 — 지표·구조 재편 (08/01~05)</t>
+          <t>[완료] 7단계 — 지표·구조 재편 (08/01~06)</t>
         </is>
       </c>
       <c r="B19" s="11" t="n"/>
@@ -1520,36 +1520,40 @@
       <c r="L25" s="15" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>v1 마무리 — 인사이트용 (8월 마감 목표)</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="13" t="n"/>
-      <c r="H26" s="13" t="n"/>
-      <c r="I26" s="13" t="n"/>
-      <c r="J26" s="13" t="n"/>
-      <c r="K26" s="13" t="n"/>
-      <c r="L26" s="13" t="n"/>
-      <c r="M26" s="13" t="n"/>
-      <c r="N26" s="13" t="n"/>
-      <c r="O26" s="13" t="n"/>
-      <c r="P26" s="13" t="n"/>
-      <c r="Q26" s="13" t="n"/>
-      <c r="R26" s="13" t="n"/>
-      <c r="S26" s="13" t="n"/>
-      <c r="T26" s="13" t="n"/>
+      <c r="A26" s="15" t="n"/>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>대시보드 채널 비교·비중 — 3개월 공통 기간·월별 그룹 막대 전환</t>
+        </is>
+      </c>
+      <c r="C26" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="D26" s="41" t="inlineStr">
+        <is>
+          <t>AI 협업</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>08-05</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="15" t="n"/>
+      <c r="H26" s="15" t="n"/>
+      <c r="I26" s="15" t="n"/>
+      <c r="J26" s="42" t="n"/>
+      <c r="K26" s="15" t="n"/>
+      <c r="L26" s="15" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="15" t="n"/>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>사용자 권한 페이지 정리 — 목 매트릭스 제거·역할별 권한 안내</t>
+          <t>파이프라인 개편(월 신규 문의 중심) + 90일 무활동 자동 보류(운영 80건)</t>
         </is>
       </c>
       <c r="C27" s="40" t="inlineStr">
@@ -1564,7 +1568,7 @@
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>08-05</t>
+          <t>08-06</t>
         </is>
       </c>
       <c r="F27" s="15" t="n"/>
@@ -1576,40 +1580,36 @@
       <c r="L27" s="15" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>대시보드/분석 역할 분리 — 중복 위젯 4종 정리·딥링크</t>
-        </is>
-      </c>
-      <c r="C28" s="40" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="D28" s="41" t="inlineStr">
-        <is>
-          <t>AI 협업</t>
-        </is>
-      </c>
-      <c r="E28" s="15" t="inlineStr">
-        <is>
-          <t>08-06</t>
-        </is>
-      </c>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
-      <c r="H28" s="15" t="n"/>
-      <c r="I28" s="15" t="n"/>
-      <c r="J28" s="42" t="n"/>
-      <c r="K28" s="15" t="n"/>
-      <c r="L28" s="15" t="n"/>
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>v1 마무리 — 인사이트용 (8월 마감 목표)</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="13" t="n"/>
+      <c r="H28" s="13" t="n"/>
+      <c r="I28" s="13" t="n"/>
+      <c r="J28" s="13" t="n"/>
+      <c r="K28" s="13" t="n"/>
+      <c r="L28" s="13" t="n"/>
+      <c r="M28" s="13" t="n"/>
+      <c r="N28" s="13" t="n"/>
+      <c r="O28" s="13" t="n"/>
+      <c r="P28" s="13" t="n"/>
+      <c r="Q28" s="13" t="n"/>
+      <c r="R28" s="13" t="n"/>
+      <c r="S28" s="13" t="n"/>
+      <c r="T28" s="13" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="15" t="n"/>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>코호트 위젯 표현 개선 — 시간축 세로 막대·% 상시 표기</t>
+          <t>사용자 권한 페이지 정리 — 목 매트릭스 제거·역할별 권한 안내</t>
         </is>
       </c>
       <c r="C29" s="40" t="inlineStr">
@@ -1639,12 +1639,12 @@
       <c r="A30" s="15" t="n"/>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>외부 매출 연동 — 파일 업로드(선행) → 시트 연동</t>
-        </is>
-      </c>
-      <c r="C30" s="43" t="inlineStr">
-        <is>
-          <t>보류</t>
+          <t>대시보드/분석 역할 분리 — 중복 위젯 4종 정리·딥링크</t>
+        </is>
+      </c>
+      <c r="C30" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="D30" s="41" t="inlineStr">
@@ -1654,99 +1654,87 @@
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>보안 검토 완료·재개 시 착수(투두 #45)</t>
+          <t>08-06</t>
         </is>
       </c>
       <c r="F30" s="15" t="n"/>
       <c r="G30" s="15" t="n"/>
       <c r="H30" s="15" t="n"/>
       <c r="I30" s="15" t="n"/>
-      <c r="J30" s="15" t="n"/>
+      <c r="J30" s="42" t="n"/>
       <c r="K30" s="15" t="n"/>
       <c r="L30" s="15" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="14" t="n"/>
+      <c r="A31" s="15" t="n"/>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>미입력 매출 5건 확정 입력</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>대기</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
+          <t>코호트 위젯 표현 개선 — 시간축 세로 막대·% 상시 표기</t>
+        </is>
+      </c>
+      <c r="C31" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="D31" s="41" t="inlineStr">
         <is>
           <t>AI 협업</t>
         </is>
       </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>확정 자료 수급 대기</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="14" t="n"/>
-      <c r="H31" s="14" t="n"/>
-      <c r="I31" s="14" t="n"/>
-      <c r="J31" s="21" t="n"/>
-      <c r="K31" s="21" t="n"/>
-      <c r="L31" s="14" t="n"/>
-      <c r="M31" s="14" t="n"/>
-      <c r="N31" s="14" t="n"/>
-      <c r="O31" s="14" t="n"/>
-      <c r="P31" s="14" t="n"/>
-      <c r="Q31" s="14" t="n"/>
-      <c r="R31" s="14" t="n"/>
-      <c r="S31" s="14" t="n"/>
-      <c r="T31" s="14" t="n"/>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>08-05</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
+      <c r="H31" s="15" t="n"/>
+      <c r="I31" s="15" t="n"/>
+      <c r="J31" s="42" t="n"/>
+      <c r="K31" s="15" t="n"/>
+      <c r="L31" s="15" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="14" t="n"/>
+      <c r="A32" s="15" t="n"/>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>매출 자료 파서 고도화 — 카테고리 자동 추출·보고서 수익 반영</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
+          <t>외부 매출 연동 — 파일 업로드(선행) → 시트 연동</t>
+        </is>
+      </c>
+      <c r="C32" s="43" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="D32" s="41" t="inlineStr">
         <is>
           <t>AI 협업</t>
         </is>
       </c>
-      <c r="E32" s="18" t="inlineStr"/>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="14" t="n"/>
-      <c r="H32" s="14" t="n"/>
-      <c r="I32" s="14" t="n"/>
-      <c r="J32" s="21" t="n"/>
-      <c r="K32" s="21" t="n"/>
-      <c r="L32" s="21" t="n"/>
-      <c r="M32" s="14" t="n"/>
-      <c r="N32" s="14" t="n"/>
-      <c r="O32" s="14" t="n"/>
-      <c r="P32" s="14" t="n"/>
-      <c r="Q32" s="14" t="n"/>
-      <c r="R32" s="14" t="n"/>
-      <c r="S32" s="14" t="n"/>
-      <c r="T32" s="14" t="n"/>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>보안 검토 완료·재개 시 착수(투두 #45)</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
+      <c r="H32" s="15" t="n"/>
+      <c r="I32" s="15" t="n"/>
+      <c r="J32" s="15" t="n"/>
+      <c r="K32" s="15" t="n"/>
+      <c r="L32" s="15" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="14" t="n"/>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>백업 외부 복제(서버 외부 보관)</t>
+          <t>미입력 매출 5건 확정 입력</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>대기</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
@@ -1754,7 +1742,11 @@
           <t>AI 협업</t>
         </is>
       </c>
-      <c r="E33" s="18" t="inlineStr"/>
+      <c r="E33" s="18" t="inlineStr">
+        <is>
+          <t>확정 자료 수급 대기</t>
+        </is>
+      </c>
       <c r="F33" s="14" t="n"/>
       <c r="G33" s="14" t="n"/>
       <c r="H33" s="14" t="n"/>
@@ -1773,18 +1765,30 @@
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="14" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="12" t="n"/>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>매출 자료 파서 고도화 — 카테고리 자동 추출·보고서 수익 반영</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>AI 협업</t>
+        </is>
+      </c>
+      <c r="E34" s="18" t="inlineStr"/>
       <c r="F34" s="14" t="n"/>
       <c r="G34" s="14" t="n"/>
       <c r="H34" s="14" t="n"/>
       <c r="I34" s="14" t="n"/>
-      <c r="J34" s="14" t="n"/>
+      <c r="J34" s="21" t="n"/>
       <c r="K34" s="21" t="n"/>
       <c r="L34" s="21" t="n"/>
-      <c r="M34" s="21" t="n"/>
+      <c r="M34" s="14" t="n"/>
       <c r="N34" s="14" t="n"/>
       <c r="O34" s="14" t="n"/>
       <c r="P34" s="14" t="n"/>
@@ -1797,7 +1801,7 @@
       <c r="A35" s="14" t="n"/>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>팀 사용 피드백 반영·화면 다듬기</t>
+          <t>백업 외부 복제(서버 외부 보관)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -1810,20 +1814,16 @@
           <t>AI 협업</t>
         </is>
       </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t>운영 중 수시</t>
-        </is>
-      </c>
+      <c r="E35" s="18" t="inlineStr"/>
       <c r="F35" s="14" t="n"/>
       <c r="G35" s="14" t="n"/>
       <c r="H35" s="14" t="n"/>
       <c r="I35" s="14" t="n"/>
       <c r="J35" s="21" t="n"/>
       <c r="K35" s="21" t="n"/>
-      <c r="L35" s="21" t="n"/>
-      <c r="M35" s="21" t="n"/>
-      <c r="N35" s="21" t="n"/>
+      <c r="L35" s="14" t="n"/>
+      <c r="M35" s="14" t="n"/>
+      <c r="N35" s="14" t="n"/>
       <c r="O35" s="14" t="n"/>
       <c r="P35" s="14" t="n"/>
       <c r="Q35" s="14" t="n"/>
@@ -1833,31 +1833,19 @@
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="14" t="n"/>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>8월 월간 데이터 갱신 사이클 1회 완주(절차 최종 검증)</t>
-        </is>
-      </c>
-      <c r="C36" s="20" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>AI 협업</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr"/>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="12" t="n"/>
       <c r="F36" s="14" t="n"/>
       <c r="G36" s="14" t="n"/>
       <c r="H36" s="14" t="n"/>
       <c r="I36" s="14" t="n"/>
       <c r="J36" s="14" t="n"/>
-      <c r="K36" s="14" t="n"/>
-      <c r="L36" s="14" t="n"/>
-      <c r="M36" s="14" t="n"/>
-      <c r="N36" s="21" t="n"/>
+      <c r="K36" s="21" t="n"/>
+      <c r="L36" s="21" t="n"/>
+      <c r="M36" s="21" t="n"/>
+      <c r="N36" s="14" t="n"/>
       <c r="O36" s="14" t="n"/>
       <c r="P36" s="14" t="n"/>
       <c r="Q36" s="14" t="n"/>
@@ -1869,7 +1857,7 @@
       <c r="A37" s="14" t="n"/>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>v1 마감 — 운영 안정판 확정·문서 정리</t>
+          <t>팀 사용 피드백 반영·화면 다듬기</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
@@ -1884,19 +1872,19 @@
       </c>
       <c r="E37" s="18" t="inlineStr">
         <is>
-          <t>9월 초 목표</t>
+          <t>운영 중 수시</t>
         </is>
       </c>
       <c r="F37" s="14" t="n"/>
       <c r="G37" s="14" t="n"/>
       <c r="H37" s="14" t="n"/>
       <c r="I37" s="14" t="n"/>
-      <c r="J37" s="14" t="n"/>
-      <c r="K37" s="14" t="n"/>
-      <c r="L37" s="14" t="n"/>
-      <c r="M37" s="14" t="n"/>
+      <c r="J37" s="21" t="n"/>
+      <c r="K37" s="21" t="n"/>
+      <c r="L37" s="21" t="n"/>
+      <c r="M37" s="21" t="n"/>
       <c r="N37" s="21" t="n"/>
-      <c r="O37" s="21" t="n"/>
+      <c r="O37" s="14" t="n"/>
       <c r="P37" s="14" t="n"/>
       <c r="Q37" s="14" t="n"/>
       <c r="R37" s="14" t="n"/>
@@ -1904,141 +1892,137 @@
       <c r="T37" s="14" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>v2-A — 인사이트용 고도화 (2차 출시 검토 항목)</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="12" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="13" t="n"/>
-      <c r="H38" s="13" t="n"/>
-      <c r="I38" s="13" t="n"/>
-      <c r="J38" s="13" t="n"/>
-      <c r="K38" s="13" t="n"/>
-      <c r="L38" s="13" t="n"/>
-      <c r="M38" s="13" t="n"/>
-      <c r="N38" s="13" t="n"/>
-      <c r="O38" s="13" t="n"/>
-      <c r="P38" s="13" t="n"/>
-      <c r="Q38" s="13" t="n"/>
-      <c r="R38" s="13" t="n"/>
-      <c r="S38" s="13" t="n"/>
-      <c r="T38" s="13" t="n"/>
+      <c r="A38" s="14" t="n"/>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>8월 월간 데이터 갱신 사이클 1회 완주(절차 최종 검증)</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>AI 협업</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="inlineStr"/>
+      <c r="F38" s="14" t="n"/>
+      <c r="G38" s="14" t="n"/>
+      <c r="H38" s="14" t="n"/>
+      <c r="I38" s="14" t="n"/>
+      <c r="J38" s="14" t="n"/>
+      <c r="K38" s="14" t="n"/>
+      <c r="L38" s="14" t="n"/>
+      <c r="M38" s="14" t="n"/>
+      <c r="N38" s="21" t="n"/>
+      <c r="O38" s="14" t="n"/>
+      <c r="P38" s="14" t="n"/>
+      <c r="Q38" s="14" t="n"/>
+      <c r="R38" s="14" t="n"/>
+      <c r="S38" s="14" t="n"/>
+      <c r="T38" s="14" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="14" t="n"/>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>[선행] 실사용 데이터 축적 3개월</t>
-        </is>
-      </c>
-      <c r="C39" s="22" t="inlineStr">
-        <is>
-          <t>진행 중</t>
+          <t>v1 마감 — 운영 안정판 확정·문서 정리</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>예정</t>
         </is>
       </c>
       <c r="D39" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AI 협업</t>
         </is>
       </c>
       <c r="E39" s="18" t="inlineStr">
         <is>
-          <t>7월 실가동 기준 → 10월 충족</t>
+          <t>9월 초 목표</t>
         </is>
       </c>
       <c r="F39" s="14" t="n"/>
-      <c r="G39" s="23" t="n"/>
-      <c r="H39" s="23" t="n"/>
-      <c r="I39" s="23" t="n"/>
-      <c r="J39" s="23" t="n"/>
-      <c r="K39" s="23" t="n"/>
-      <c r="L39" s="23" t="n"/>
-      <c r="M39" s="23" t="n"/>
-      <c r="N39" s="23" t="n"/>
-      <c r="O39" s="23" t="n"/>
-      <c r="P39" s="23" t="n"/>
+      <c r="G39" s="14" t="n"/>
+      <c r="H39" s="14" t="n"/>
+      <c r="I39" s="14" t="n"/>
+      <c r="J39" s="14" t="n"/>
+      <c r="K39" s="14" t="n"/>
+      <c r="L39" s="14" t="n"/>
+      <c r="M39" s="14" t="n"/>
+      <c r="N39" s="21" t="n"/>
+      <c r="O39" s="21" t="n"/>
+      <c r="P39" s="14" t="n"/>
       <c r="Q39" s="14" t="n"/>
       <c r="R39" s="14" t="n"/>
       <c r="S39" s="14" t="n"/>
       <c r="T39" s="14" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="14" t="n"/>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>[선행] 행동 데이터 수집 설계(문의 횟수·단계 이동 패턴)</t>
-        </is>
-      </c>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>계획</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr">
-        <is>
-          <t>AI 협업</t>
-        </is>
-      </c>
-      <c r="E40" s="18" t="inlineStr">
-        <is>
-          <t>축적 데이터 기반</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="n"/>
-      <c r="G40" s="14" t="n"/>
-      <c r="H40" s="14" t="n"/>
-      <c r="I40" s="14" t="n"/>
-      <c r="J40" s="14" t="n"/>
-      <c r="K40" s="14" t="n"/>
-      <c r="L40" s="14" t="n"/>
-      <c r="M40" s="14" t="n"/>
-      <c r="N40" s="14" t="n"/>
-      <c r="O40" s="25" t="n"/>
-      <c r="P40" s="25" t="n"/>
-      <c r="Q40" s="14" t="n"/>
-      <c r="R40" s="14" t="n"/>
-      <c r="S40" s="14" t="n"/>
-      <c r="T40" s="14" t="n"/>
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>v2-A — 인사이트용 고도화 (2차 출시 검토 항목)</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="13" t="n"/>
+      <c r="G40" s="13" t="n"/>
+      <c r="H40" s="13" t="n"/>
+      <c r="I40" s="13" t="n"/>
+      <c r="J40" s="13" t="n"/>
+      <c r="K40" s="13" t="n"/>
+      <c r="L40" s="13" t="n"/>
+      <c r="M40" s="13" t="n"/>
+      <c r="N40" s="13" t="n"/>
+      <c r="O40" s="13" t="n"/>
+      <c r="P40" s="13" t="n"/>
+      <c r="Q40" s="13" t="n"/>
+      <c r="R40" s="13" t="n"/>
+      <c r="S40" s="13" t="n"/>
+      <c r="T40" s="13" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="14" t="n"/>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>광고 성과 귀속 고도화 — 채널·캠페인별 수익 분해</t>
-        </is>
-      </c>
-      <c r="C41" s="24" t="inlineStr">
-        <is>
-          <t>계획</t>
+          <t>[선행] 실사용 데이터 축적 3개월</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>진행 중</t>
         </is>
       </c>
       <c r="D41" s="17" t="inlineStr">
         <is>
-          <t>AI 협업</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr">
         <is>
-          <t>문의의 광고 출처 증거(UTM) 축적 필요</t>
+          <t>7월 실가동 기준 → 10월 충족</t>
         </is>
       </c>
       <c r="F41" s="14" t="n"/>
-      <c r="G41" s="14" t="n"/>
-      <c r="H41" s="14" t="n"/>
-      <c r="I41" s="14" t="n"/>
-      <c r="J41" s="14" t="n"/>
-      <c r="K41" s="14" t="n"/>
-      <c r="L41" s="14" t="n"/>
-      <c r="M41" s="14" t="n"/>
-      <c r="N41" s="14" t="n"/>
-      <c r="O41" s="25" t="n"/>
-      <c r="P41" s="25" t="n"/>
-      <c r="Q41" s="25" t="n"/>
+      <c r="G41" s="23" t="n"/>
+      <c r="H41" s="23" t="n"/>
+      <c r="I41" s="23" t="n"/>
+      <c r="J41" s="23" t="n"/>
+      <c r="K41" s="23" t="n"/>
+      <c r="L41" s="23" t="n"/>
+      <c r="M41" s="23" t="n"/>
+      <c r="N41" s="23" t="n"/>
+      <c r="O41" s="23" t="n"/>
+      <c r="P41" s="23" t="n"/>
+      <c r="Q41" s="14" t="n"/>
       <c r="R41" s="14" t="n"/>
       <c r="S41" s="14" t="n"/>
       <c r="T41" s="14" t="n"/>
@@ -2047,7 +2031,7 @@
       <c r="A42" s="14" t="n"/>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>잠재고객 자동 점수화·우선순위 지정(리드 스코어링)</t>
+          <t>[선행] 행동 데이터 수집 설계(문의 횟수·단계 이동 패턴)</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
@@ -2062,7 +2046,7 @@
       </c>
       <c r="E42" s="18" t="inlineStr">
         <is>
-          <t>2차 출시 검토 항목</t>
+          <t>축적 데이터 기반</t>
         </is>
       </c>
       <c r="F42" s="14" t="n"/>
@@ -2074,10 +2058,10 @@
       <c r="L42" s="14" t="n"/>
       <c r="M42" s="14" t="n"/>
       <c r="N42" s="14" t="n"/>
-      <c r="O42" s="14" t="n"/>
-      <c r="P42" s="14" t="n"/>
-      <c r="Q42" s="25" t="n"/>
-      <c r="R42" s="25" t="n"/>
+      <c r="O42" s="25" t="n"/>
+      <c r="P42" s="25" t="n"/>
+      <c r="Q42" s="14" t="n"/>
+      <c r="R42" s="14" t="n"/>
       <c r="S42" s="14" t="n"/>
       <c r="T42" s="14" t="n"/>
     </row>
@@ -2085,7 +2069,7 @@
       <c r="A43" s="14" t="n"/>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>개인화 커뮤니케이션 도구(세그먼트 메시지·알림톡)</t>
+          <t>광고 성과 귀속 고도화 — 채널·캠페인별 수익 분해</t>
         </is>
       </c>
       <c r="C43" s="24" t="inlineStr">
@@ -2100,7 +2084,7 @@
       </c>
       <c r="E43" s="18" t="inlineStr">
         <is>
-          <t>2차 출시 검토 항목</t>
+          <t>문의의 광고 출처 증거(UTM) 축적 필요</t>
         </is>
       </c>
       <c r="F43" s="14" t="n"/>
@@ -2112,18 +2096,18 @@
       <c r="L43" s="14" t="n"/>
       <c r="M43" s="14" t="n"/>
       <c r="N43" s="14" t="n"/>
-      <c r="O43" s="14" t="n"/>
-      <c r="P43" s="14" t="n"/>
-      <c r="Q43" s="14" t="n"/>
-      <c r="R43" s="25" t="n"/>
-      <c r="S43" s="25" t="n"/>
+      <c r="O43" s="25" t="n"/>
+      <c r="P43" s="25" t="n"/>
+      <c r="Q43" s="25" t="n"/>
+      <c r="R43" s="14" t="n"/>
+      <c r="S43" s="14" t="n"/>
       <c r="T43" s="14" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="14" t="n"/>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>보고서 고도화(PDF 서버 생성·차트 고정 저장) · 권한 세분화</t>
+          <t>잠재고객 자동 점수화·우선순위 지정(리드 스코어링)</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
@@ -2136,7 +2120,11 @@
           <t>AI 협업</t>
         </is>
       </c>
-      <c r="E44" s="18" t="inlineStr"/>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>2차 출시 검토 항목</t>
+        </is>
+      </c>
       <c r="F44" s="14" t="n"/>
       <c r="G44" s="14" t="n"/>
       <c r="H44" s="14" t="n"/>
@@ -2154,112 +2142,108 @@
       <c r="T44" s="14" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>v2-B — 병원용 신규 (인사이트용을 프로토타입으로, 내부팀 직접 개발 · AI 코딩 제외)</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="11" t="n"/>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="12" t="n"/>
-      <c r="F45" s="13" t="n"/>
-      <c r="G45" s="13" t="n"/>
-      <c r="H45" s="13" t="n"/>
-      <c r="I45" s="13" t="n"/>
-      <c r="J45" s="13" t="n"/>
-      <c r="K45" s="13" t="n"/>
-      <c r="L45" s="13" t="n"/>
-      <c r="M45" s="13" t="n"/>
-      <c r="N45" s="13" t="n"/>
-      <c r="O45" s="13" t="n"/>
-      <c r="P45" s="13" t="n"/>
-      <c r="Q45" s="13" t="n"/>
-      <c r="R45" s="13" t="n"/>
-      <c r="S45" s="13" t="n"/>
-      <c r="T45" s="13" t="n"/>
+      <c r="A45" s="14" t="n"/>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>개인화 커뮤니케이션 도구(세그먼트 메시지·알림톡)</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>계획</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t>AI 협업</t>
+        </is>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
+        <is>
+          <t>2차 출시 검토 항목</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="n"/>
+      <c r="G45" s="14" t="n"/>
+      <c r="H45" s="14" t="n"/>
+      <c r="I45" s="14" t="n"/>
+      <c r="J45" s="14" t="n"/>
+      <c r="K45" s="14" t="n"/>
+      <c r="L45" s="14" t="n"/>
+      <c r="M45" s="14" t="n"/>
+      <c r="N45" s="14" t="n"/>
+      <c r="O45" s="14" t="n"/>
+      <c r="P45" s="14" t="n"/>
+      <c r="Q45" s="14" t="n"/>
+      <c r="R45" s="25" t="n"/>
+      <c r="S45" s="25" t="n"/>
+      <c r="T45" s="14" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="14" t="n"/>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>① 병의원 적합화 검토 — 기능 갭 분석(고객 개체·퍼널·규제·지표)</t>
-        </is>
-      </c>
-      <c r="C46" s="26" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>보고서 고도화(PDF 서버 생성·차트 고정 저장) · 권한 세분화</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>계획</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
         <is>
-          <t>AI 협업+내부팀</t>
-        </is>
-      </c>
-      <c r="E46" s="18" t="inlineStr">
-        <is>
-          <t>'병원용 변경 검토' 탭이 출발점</t>
-        </is>
-      </c>
+          <t>AI 협업</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr"/>
       <c r="F46" s="14" t="n"/>
       <c r="G46" s="14" t="n"/>
       <c r="H46" s="14" t="n"/>
       <c r="I46" s="14" t="n"/>
-      <c r="J46" s="27" t="n"/>
-      <c r="K46" s="27" t="n"/>
-      <c r="L46" s="27" t="n"/>
-      <c r="M46" s="27" t="n"/>
-      <c r="N46" s="27" t="n"/>
+      <c r="J46" s="14" t="n"/>
+      <c r="K46" s="14" t="n"/>
+      <c r="L46" s="14" t="n"/>
+      <c r="M46" s="14" t="n"/>
+      <c r="N46" s="14" t="n"/>
       <c r="O46" s="14" t="n"/>
       <c r="P46" s="14" t="n"/>
-      <c r="Q46" s="14" t="n"/>
-      <c r="R46" s="14" t="n"/>
+      <c r="Q46" s="25" t="n"/>
+      <c r="R46" s="25" t="n"/>
       <c r="S46" s="14" t="n"/>
       <c r="T46" s="14" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="n"/>
-      <c r="B47" s="15" t="inlineStr">
-        <is>
-          <t>② 프로토타입 인계 패키지 — 화면·API 명세·도메인 규칙 문서화</t>
-        </is>
-      </c>
-      <c r="C47" s="26" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="D47" s="17" t="inlineStr">
-        <is>
-          <t>AI 협업</t>
-        </is>
-      </c>
-      <c r="E47" s="18" t="inlineStr">
-        <is>
-          <t>인사이트용 = 프로토타입</t>
-        </is>
-      </c>
-      <c r="F47" s="14" t="n"/>
-      <c r="G47" s="14" t="n"/>
-      <c r="H47" s="14" t="n"/>
-      <c r="I47" s="14" t="n"/>
-      <c r="J47" s="14" t="n"/>
-      <c r="K47" s="27" t="n"/>
-      <c r="L47" s="27" t="n"/>
-      <c r="M47" s="27" t="n"/>
-      <c r="N47" s="27" t="n"/>
-      <c r="O47" s="27" t="n"/>
-      <c r="P47" s="14" t="n"/>
-      <c r="Q47" s="14" t="n"/>
-      <c r="R47" s="14" t="n"/>
-      <c r="S47" s="14" t="n"/>
-      <c r="T47" s="14" t="n"/>
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>v2-B — 병원용 신규 (인사이트용을 프로토타입으로, 내부팀 직접 개발 · AI 코딩 제외)</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="11" t="n"/>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="13" t="n"/>
+      <c r="G47" s="13" t="n"/>
+      <c r="H47" s="13" t="n"/>
+      <c r="I47" s="13" t="n"/>
+      <c r="J47" s="13" t="n"/>
+      <c r="K47" s="13" t="n"/>
+      <c r="L47" s="13" t="n"/>
+      <c r="M47" s="13" t="n"/>
+      <c r="N47" s="13" t="n"/>
+      <c r="O47" s="13" t="n"/>
+      <c r="P47" s="13" t="n"/>
+      <c r="Q47" s="13" t="n"/>
+      <c r="R47" s="13" t="n"/>
+      <c r="S47" s="13" t="n"/>
+      <c r="T47" s="13" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="14" t="n"/>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>③ 병원용 요구사항 확정 (변경사항 우선순위 확정)</t>
+          <t>① 병의원 적합화 검토 — 기능 갭 분석(고객 개체·퍼널·규제·지표)</t>
         </is>
       </c>
       <c r="C48" s="26" t="inlineStr">
@@ -2269,24 +2253,24 @@
       </c>
       <c r="D48" s="17" t="inlineStr">
         <is>
-          <t>내부 디자인·개발팀</t>
+          <t>AI 협업+내부팀</t>
         </is>
       </c>
       <c r="E48" s="18" t="inlineStr">
         <is>
-          <t>①·② 산출물 기반</t>
+          <t>'병원용 변경 검토' 탭이 출발점</t>
         </is>
       </c>
       <c r="F48" s="14" t="n"/>
       <c r="G48" s="14" t="n"/>
       <c r="H48" s="14" t="n"/>
       <c r="I48" s="14" t="n"/>
-      <c r="J48" s="14" t="n"/>
-      <c r="K48" s="14" t="n"/>
-      <c r="L48" s="14" t="n"/>
-      <c r="M48" s="14" t="n"/>
-      <c r="N48" s="14" t="n"/>
-      <c r="O48" s="27" t="n"/>
+      <c r="J48" s="27" t="n"/>
+      <c r="K48" s="27" t="n"/>
+      <c r="L48" s="27" t="n"/>
+      <c r="M48" s="27" t="n"/>
+      <c r="N48" s="27" t="n"/>
+      <c r="O48" s="14" t="n"/>
       <c r="P48" s="14" t="n"/>
       <c r="Q48" s="14" t="n"/>
       <c r="R48" s="14" t="n"/>
@@ -2297,7 +2281,7 @@
       <c r="A49" s="14" t="n"/>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>④ 병원용 UI/UX 디자인 (프로토타입 기반 재설계)</t>
+          <t>② 프로토타입 인계 패키지 — 화면·API 명세·도메인 규칙 문서화</t>
         </is>
       </c>
       <c r="C49" s="26" t="inlineStr">
@@ -2307,12 +2291,12 @@
       </c>
       <c r="D49" s="17" t="inlineStr">
         <is>
-          <t>내부 디자인팀</t>
+          <t>AI 협업</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr">
         <is>
-          <t>환자·예약 중심 화면</t>
+          <t>인사이트용 = 프로토타입</t>
         </is>
       </c>
       <c r="F49" s="14" t="n"/>
@@ -2320,12 +2304,12 @@
       <c r="H49" s="14" t="n"/>
       <c r="I49" s="14" t="n"/>
       <c r="J49" s="14" t="n"/>
-      <c r="K49" s="14" t="n"/>
-      <c r="L49" s="14" t="n"/>
-      <c r="M49" s="14" t="n"/>
-      <c r="N49" s="14" t="n"/>
+      <c r="K49" s="27" t="n"/>
+      <c r="L49" s="27" t="n"/>
+      <c r="M49" s="27" t="n"/>
+      <c r="N49" s="27" t="n"/>
       <c r="O49" s="27" t="n"/>
-      <c r="P49" s="27" t="n"/>
+      <c r="P49" s="14" t="n"/>
       <c r="Q49" s="14" t="n"/>
       <c r="R49" s="14" t="n"/>
       <c r="S49" s="14" t="n"/>
@@ -2335,7 +2319,7 @@
       <c r="A50" s="14" t="n"/>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>⑤ 병원용 개발 — 직접 프로그래밍 (AI 바이브 코딩 제외)</t>
+          <t>③ 병원용 요구사항 확정 (변경사항 우선순위 확정)</t>
         </is>
       </c>
       <c r="C50" s="26" t="inlineStr">
@@ -2345,12 +2329,12 @@
       </c>
       <c r="D50" s="17" t="inlineStr">
         <is>
-          <t>내부 개발팀</t>
+          <t>내부 디자인·개발팀</t>
         </is>
       </c>
       <c r="E50" s="18" t="inlineStr">
         <is>
-          <t>변경사항 순차 적용</t>
+          <t>①·② 산출물 기반</t>
         </is>
       </c>
       <c r="F50" s="14" t="n"/>
@@ -2362,18 +2346,18 @@
       <c r="L50" s="14" t="n"/>
       <c r="M50" s="14" t="n"/>
       <c r="N50" s="14" t="n"/>
-      <c r="O50" s="14" t="n"/>
-      <c r="P50" s="27" t="n"/>
-      <c r="Q50" s="27" t="n"/>
-      <c r="R50" s="27" t="n"/>
-      <c r="S50" s="27" t="n"/>
+      <c r="O50" s="27" t="n"/>
+      <c r="P50" s="14" t="n"/>
+      <c r="Q50" s="14" t="n"/>
+      <c r="R50" s="14" t="n"/>
+      <c r="S50" s="14" t="n"/>
       <c r="T50" s="14" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="14" t="n"/>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>⑥ 파일럿 병원 적용·피드백 반영</t>
+          <t>④ 병원용 UI/UX 디자인 (프로토타입 기반 재설계)</t>
         </is>
       </c>
       <c r="C51" s="26" t="inlineStr">
@@ -2383,12 +2367,12 @@
       </c>
       <c r="D51" s="17" t="inlineStr">
         <is>
-          <t>내부 디자인·개발팀</t>
+          <t>내부 디자인팀</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr">
         <is>
-          <t>1~2개 병원</t>
+          <t>환자·예약 중심 화면</t>
         </is>
       </c>
       <c r="F51" s="14" t="n"/>
@@ -2400,18 +2384,18 @@
       <c r="L51" s="14" t="n"/>
       <c r="M51" s="14" t="n"/>
       <c r="N51" s="14" t="n"/>
-      <c r="O51" s="14" t="n"/>
-      <c r="P51" s="14" t="n"/>
+      <c r="O51" s="27" t="n"/>
+      <c r="P51" s="27" t="n"/>
       <c r="Q51" s="14" t="n"/>
       <c r="R51" s="14" t="n"/>
-      <c r="S51" s="27" t="n"/>
+      <c r="S51" s="14" t="n"/>
       <c r="T51" s="14" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="14" t="n"/>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>⑦ 병원용 출시</t>
+          <t>⑤ 병원용 개발 — 직접 프로그래밍 (AI 바이브 코딩 제외)</t>
         </is>
       </c>
       <c r="C52" s="26" t="inlineStr">
@@ -2421,12 +2405,12 @@
       </c>
       <c r="D52" s="17" t="inlineStr">
         <is>
-          <t>내부 디자인·개발팀</t>
+          <t>내부 개발팀</t>
         </is>
       </c>
       <c r="E52" s="18" t="inlineStr">
         <is>
-          <t>파일럿 통과 후</t>
+          <t>변경사항 순차 적용</t>
         </is>
       </c>
       <c r="F52" s="14" t="n"/>
@@ -2439,42 +2423,119 @@
       <c r="M52" s="14" t="n"/>
       <c r="N52" s="14" t="n"/>
       <c r="O52" s="14" t="n"/>
-      <c r="P52" s="14" t="n"/>
-      <c r="Q52" s="14" t="n"/>
-      <c r="R52" s="14" t="n"/>
-      <c r="S52" s="14" t="n"/>
-      <c r="T52" s="27" t="n"/>
+      <c r="P52" s="27" t="n"/>
+      <c r="Q52" s="27" t="n"/>
+      <c r="R52" s="27" t="n"/>
+      <c r="S52" s="27" t="n"/>
+      <c r="T52" s="14" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="n"/>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>⑥ 파일럿 병원 적용·피드백 반영</t>
+        </is>
+      </c>
+      <c r="C53" s="26" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="D53" s="17" t="inlineStr">
+        <is>
+          <t>내부 디자인·개발팀</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>1~2개 병원</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="n"/>
+      <c r="G53" s="14" t="n"/>
+      <c r="H53" s="14" t="n"/>
+      <c r="I53" s="14" t="n"/>
+      <c r="J53" s="14" t="n"/>
+      <c r="K53" s="14" t="n"/>
+      <c r="L53" s="14" t="n"/>
+      <c r="M53" s="14" t="n"/>
+      <c r="N53" s="14" t="n"/>
+      <c r="O53" s="14" t="n"/>
+      <c r="P53" s="14" t="n"/>
+      <c r="Q53" s="14" t="n"/>
+      <c r="R53" s="14" t="n"/>
+      <c r="S53" s="27" t="n"/>
+      <c r="T53" s="14" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="28" t="inlineStr">
-        <is>
-          <t>※ 완료 구간은 실제 완료된 주 기준. 예정 구간은 잠정 일정 — 자료 수급·내부팀 리소스에 따라 조정.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="28" t="inlineStr">
-        <is>
-          <t>※ v2-A(인사이트용)와 v2-B(병원용)는 동시 진행. 병원용은 인사이트용을 프로토타입으로 내부 디자인·개발팀이 직접 프로그래밍(AI 바이브 코딩 제외).</t>
-        </is>
-      </c>
-    </row>
+      <c r="A54" s="14" t="n"/>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>⑦ 병원용 출시</t>
+        </is>
+      </c>
+      <c r="C54" s="26" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>내부 디자인·개발팀</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="inlineStr">
+        <is>
+          <t>파일럿 통과 후</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="n"/>
+      <c r="G54" s="14" t="n"/>
+      <c r="H54" s="14" t="n"/>
+      <c r="I54" s="14" t="n"/>
+      <c r="J54" s="14" t="n"/>
+      <c r="K54" s="14" t="n"/>
+      <c r="L54" s="14" t="n"/>
+      <c r="M54" s="14" t="n"/>
+      <c r="N54" s="14" t="n"/>
+      <c r="O54" s="14" t="n"/>
+      <c r="P54" s="14" t="n"/>
+      <c r="Q54" s="14" t="n"/>
+      <c r="R54" s="14" t="n"/>
+      <c r="S54" s="14" t="n"/>
+      <c r="T54" s="27" t="n"/>
+    </row>
+    <row r="55"/>
     <row r="56">
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>※ v2-B ①②(적합화 검토·인계 패키지)는 AI 협업으로 준비 → ③부터 내부팀 주도. 변경 검토 상세는 '병원용 변경 검토' 탭.</t>
+          <t>※ 완료 구간은 실제 완료된 주 기준. 예정 구간은 잠정 일정 — 자료 수급·내부팀 리소스에 따라 조정.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="28" t="inlineStr">
         <is>
-          <t>※ 참고 자산: 구시스템(치과 CRM)이 환자 퍼널(방문→상담→예약→내원→시술→매출)·예약 관리 기능의 원형 보유 — 병원용 개발 시 재활용 가능.</t>
+          <t>※ v2-A(인사이트용)와 v2-B(병원용)는 동시 진행. 병원용은 인사이트용을 프로토타입으로 내부 디자인·개발팀이 직접 프로그래밍(AI 바이브 코딩 제외).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="28" t="inlineStr">
+        <is>
+          <t>※ v2-B ①②(적합화 검토·인계 패키지)는 AI 협업으로 준비 → ③부터 내부팀 주도. 변경 검토 상세는 '병원용 변경 검토' 탭.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="28" t="inlineStr">
+        <is>
+          <t>※ 참고 자산: 구시스템(치과 CRM)이 환자 퍼널(방문→상담→예약→내원→시술→매출)·예약 관리 기능의 원형 보유 — 병원용 개발 시 재활용 가능.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="28" t="inlineStr">
         <is>
           <t>※ 시스템 현황: 운영 서버 가동 중 · 실데이터 운영(2년치 계약 355건·광고비 12개월) · 네이버·구글·메타 3채널 광고 자동 수집.</t>
         </is>

--- a/docs/v2/진행현황-간트차트.xlsx
+++ b/docs/v2/진행현황-간트차트.xlsx
@@ -1764,30 +1764,34 @@
       <c r="T33" s="14" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="14" t="n"/>
+      <c r="A34" s="15" t="n"/>
       <c r="B34" s="15" t="inlineStr">
         <is>
           <t>매출 자료 파서 고도화 — 카테고리 자동 추출·보고서 수익 반영</t>
         </is>
       </c>
-      <c r="C34" s="20" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="C34" s="43" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="D34" s="41" t="inlineStr">
         <is>
           <t>AI 협업</t>
         </is>
       </c>
-      <c r="E34" s="18" t="inlineStr"/>
-      <c r="F34" s="14" t="n"/>
-      <c r="G34" s="14" t="n"/>
-      <c r="H34" s="14" t="n"/>
-      <c r="I34" s="14" t="n"/>
-      <c r="J34" s="21" t="n"/>
-      <c r="K34" s="21" t="n"/>
-      <c r="L34" s="21" t="n"/>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>투두 #42</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="15" t="n"/>
+      <c r="H34" s="15" t="n"/>
+      <c r="I34" s="15" t="n"/>
+      <c r="J34" s="15" t="n"/>
+      <c r="K34" s="15" t="n"/>
+      <c r="L34" s="15" t="n"/>
       <c r="M34" s="14" t="n"/>
       <c r="N34" s="14" t="n"/>
       <c r="O34" s="14" t="n"/>
@@ -2505,7 +2509,6 @@
       <c r="S54" s="14" t="n"/>
       <c r="T54" s="27" t="n"/>
     </row>
-    <row r="55"/>
     <row r="56">
       <c r="B56" s="28" t="inlineStr">
         <is>
@@ -2542,8 +2545,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A34:E34"/>
+  <mergeCells count="4">
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A6:E6"/>
